--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.53525416988253</v>
+        <v>4.636978802605912</v>
       </c>
       <c r="D2" t="n">
-        <v>25.06137843626396</v>
+        <v>4.072473995892893</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F2" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.93437278948618</v>
+        <v>9.414335578291505</v>
       </c>
       <c r="D3" t="n">
-        <v>32.05586200898028</v>
+        <v>5.209077576459295</v>
       </c>
       <c r="E3" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F3" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.24665323879378</v>
+        <v>7.677581151303989</v>
       </c>
       <c r="D4" t="n">
-        <v>39.36242627257566</v>
+        <v>6.396394269293545</v>
       </c>
       <c r="E4" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F4" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.01830463502354</v>
+        <v>7.640474503191325</v>
       </c>
       <c r="D5" t="n">
-        <v>35.70816695236494</v>
+        <v>5.802577129759303</v>
       </c>
       <c r="E5" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F5" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.85597436376766</v>
+        <v>4.851595834112245</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30774557403301</v>
+        <v>4.925008655780364</v>
       </c>
       <c r="E6" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F6" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.58755417151676</v>
+        <v>5.132977552871474</v>
       </c>
       <c r="D7" t="n">
-        <v>32.71985449612395</v>
+        <v>5.316976355620143</v>
       </c>
       <c r="E7" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F7" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.54138379401731</v>
+        <v>5.612974866527813</v>
       </c>
       <c r="D8" t="n">
-        <v>35.85661084252801</v>
+        <v>5.826699261910801</v>
       </c>
       <c r="E8" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F8" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.1852740027025</v>
+        <v>10.75510702543916</v>
       </c>
       <c r="D9" t="n">
-        <v>66.68641174456047</v>
+        <v>10.83654190849108</v>
       </c>
       <c r="E9" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F9" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.61828916307059</v>
+        <v>7.900471988998971</v>
       </c>
       <c r="D10" t="n">
-        <v>50.59987975069448</v>
+        <v>8.222480459487853</v>
       </c>
       <c r="E10" t="n">
-        <v>12.50711664318113</v>
+        <v>2.032406454516935</v>
       </c>
       <c r="F10" t="n">
-        <v>11.91949560895752</v>
+        <v>1.936918036455596</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
